--- a/files/九龙-旺角-利奥坊．曦岸.xlsx
+++ b/files/九龙-旺角-利奥坊．曦岸.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,14 +45,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -64,7 +69,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -75,7 +80,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -86,7 +91,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -96,9 +101,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -146,8 +172,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,19 +220,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,13 +238,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -608,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -23139,181 +23177,181 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>利奥坊．曦岸 - 1座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>273 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>273 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="19" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="19" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 381呎 (2房)
 $981万
@@ -23321,7 +23359,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 255呎 (2房)
 $659万
@@ -23329,7 +23367,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 382呎 (1房)
 $863万
@@ -23337,23 +23375,23 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 636呎 (3房)
-$1,650万
+$1650万
 $25,943/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 555呎 (2房)
-$1,590万
+$1590万
 $28,649/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 397呎 (2房)
 $893万
@@ -23361,29 +23399,29 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 524呎 (3房)
-$1,513万
+$1513万
 $28,874/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr"/>
-      <c r="J6" s="17" t="inlineStr"/>
-      <c r="K6" s="17" t="inlineStr"/>
-      <c r="L6" s="17" t="inlineStr"/>
-      <c r="M6" s="17" t="inlineStr"/>
-      <c r="N6" s="17" t="inlineStr"/>
-      <c r="O6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+      <c r="K5" s="21" t="inlineStr"/>
+      <c r="L5" s="21" t="inlineStr"/>
+      <c r="M5" s="21" t="inlineStr"/>
+      <c r="N5" s="21" t="inlineStr"/>
+      <c r="O5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $674万
@@ -23391,7 +23429,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $676万
@@ -23399,7 +23437,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $674万
@@ -23407,7 +23445,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $674万
@@ -23415,7 +23453,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $676万
@@ -23423,7 +23461,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $690万
@@ -23431,7 +23469,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 411呎 (2房)
 $827万
@@ -23439,7 +23477,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $539万
@@ -23447,7 +23485,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $724万
@@ -23455,7 +23493,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K7" s="16" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $661万
@@ -23463,7 +23501,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L7" s="16" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $651万
@@ -23471,7 +23509,7 @@
 (21年-04月)</t>
         </is>
       </c>
-      <c r="M7" s="16" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $510万
@@ -23479,7 +23517,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N7" s="16" t="inlineStr">
+      <c r="N6" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $528万
@@ -23487,7 +23525,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O7" s="16" t="inlineStr">
+      <c r="O6" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $384万
@@ -23496,13 +23534,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $650万
@@ -23510,7 +23548,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $672万
@@ -23518,7 +23556,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $669万
@@ -23526,7 +23564,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $669万
@@ -23534,7 +23572,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $672万
@@ -23542,7 +23580,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $645万
@@ -23550,7 +23588,7 @@
 (20年-12月)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 411呎 (2房)
 $811万
@@ -23558,7 +23596,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $535万
@@ -23566,7 +23604,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $727万
@@ -23574,7 +23612,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $678万
@@ -23582,7 +23620,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L8" s="16" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $646万
@@ -23590,7 +23628,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M8" s="16" t="inlineStr">
+      <c r="M7" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $417万
@@ -23598,7 +23636,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N8" s="16" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $525万
@@ -23606,7 +23644,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O8" s="16" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $381万
@@ -23615,13 +23653,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $645万
@@ -23629,7 +23667,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $667万
@@ -23637,7 +23675,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $665万
@@ -23645,7 +23683,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $665万
@@ -23653,7 +23691,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $667万
@@ -23661,7 +23699,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $641万
@@ -23669,7 +23707,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 411呎 (2房)
 $805万
@@ -23677,7 +23715,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $532万
@@ -23685,7 +23723,7 @@
 (21年-06月)</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $714万
@@ -23693,7 +23731,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K9" s="16" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $667万
@@ -23701,7 +23739,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $683万
@@ -23709,7 +23747,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M9" s="16" t="inlineStr">
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $526万
@@ -23717,7 +23755,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N9" s="16" t="inlineStr">
+      <c r="N8" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $527万
@@ -23725,7 +23763,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O9" s="16" t="inlineStr">
+      <c r="O8" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $379万
@@ -23734,13 +23772,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $641万
@@ -23748,7 +23786,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $663万
@@ -23756,7 +23794,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $660万
@@ -23764,7 +23802,7 @@
 (21年-07月)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $660万
@@ -23772,7 +23810,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $649万
@@ -23780,7 +23818,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $636万
@@ -23788,7 +23826,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 411呎 (2房)
 $800万
@@ -23796,7 +23834,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $528万
@@ -23804,7 +23842,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $710万
@@ -23812,7 +23850,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K10" s="16" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $655万
@@ -23820,7 +23858,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L10" s="16" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $638万
@@ -23828,7 +23866,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M10" s="16" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $528万
@@ -23836,7 +23874,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N10" s="16" t="inlineStr">
+      <c r="N9" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $518万
@@ -23844,7 +23882,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O10" s="16" t="inlineStr">
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $416万
@@ -23853,13 +23891,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $637万
@@ -23867,7 +23905,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $651万
@@ -23875,7 +23913,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $649万
@@ -23883,7 +23921,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $649万
@@ -23891,7 +23929,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $665万
@@ -23899,7 +23937,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 258呎 (1房)
 $632万
@@ -23907,7 +23945,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 411呎 (2房)
 $794万
@@ -23915,7 +23953,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $519万
@@ -23923,7 +23961,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $705万
@@ -23931,7 +23969,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K11" s="16" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $651万
@@ -23939,7 +23977,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L11" s="16" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $640万
@@ -23947,7 +23985,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M11" s="16" t="inlineStr">
+      <c r="M10" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $519万
@@ -23955,7 +23993,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N11" s="16" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $509万
@@ -23963,7 +24001,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O11" s="16" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $513万
@@ -23972,13 +24010,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $632万
@@ -23986,7 +24024,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $640万
@@ -23994,7 +24032,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $679万
@@ -24002,7 +24040,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $679万
@@ -24010,7 +24048,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $654万
@@ -24018,7 +24056,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $635万
@@ -24026,7 +24064,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 411呎 (2房)
 $800万
@@ -24034,7 +24072,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $510万
@@ -24042,7 +24080,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $700万
@@ -24050,7 +24088,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K12" s="16" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $640万
@@ -24058,7 +24096,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L12" s="16" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $629万
@@ -24066,7 +24104,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M12" s="16" t="inlineStr">
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $521万
@@ -24074,7 +24112,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N12" s="16" t="inlineStr">
+      <c r="N11" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $500万
@@ -24082,7 +24120,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O12" s="16" t="inlineStr">
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $516万
@@ -24091,13 +24129,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $628万
@@ -24105,7 +24143,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $642万
@@ -24113,7 +24151,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $640万
@@ -24121,7 +24159,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $633万
@@ -24129,7 +24167,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $642万
@@ -24137,7 +24175,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 258呎 (1房)
 $626万
@@ -24145,7 +24183,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 410呎 (2房)
 $782万
@@ -24153,7 +24191,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $506万
@@ -24161,7 +24199,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $689万
@@ -24169,7 +24207,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K13" s="16" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $642万
@@ -24177,7 +24215,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L13" s="16" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $665万
@@ -24185,7 +24223,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M13" s="16" t="inlineStr">
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $512万
@@ -24193,7 +24231,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N13" s="16" t="inlineStr">
+      <c r="N12" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $496万
@@ -24201,7 +24239,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O13" s="16" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $518万
@@ -24210,13 +24248,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $624万
@@ -24224,7 +24262,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $638万
@@ -24232,7 +24270,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $629万
@@ -24240,7 +24278,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $629万
@@ -24248,7 +24286,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $638万
@@ -24256,7 +24294,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 258呎 (1房)
 $622万
@@ -24264,7 +24302,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 410呎 (2房)
 $776万
@@ -24272,7 +24310,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $508万
@@ -24280,7 +24318,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $677万
@@ -24288,7 +24326,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K14" s="16" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $638万
@@ -24296,7 +24334,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L14" s="16" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $668万
@@ -24304,7 +24342,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M14" s="16" t="inlineStr">
+      <c r="M13" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $503万
@@ -24312,7 +24350,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N14" s="16" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $525万
@@ -24320,7 +24358,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O14" s="16" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $514万
@@ -24329,13 +24367,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $619万
@@ -24343,7 +24381,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $633万
@@ -24351,7 +24389,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $624万
@@ -24359,7 +24397,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $631万
@@ -24367,7 +24405,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $633万
@@ -24375,7 +24413,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 259呎 (1房)
 $624万
@@ -24383,7 +24421,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 410呎 (2房)
 $782万
@@ -24391,7 +24429,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $499万
@@ -24399,7 +24437,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $666万
@@ -24407,7 +24445,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K15" s="16" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $633万
@@ -24415,7 +24453,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L15" s="16" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $663万
@@ -24423,7 +24461,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M15" s="16" t="inlineStr">
+      <c r="M14" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $500万
@@ -24431,7 +24469,7 @@
 (21年-01月)</t>
         </is>
       </c>
-      <c r="N15" s="16" t="inlineStr">
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $489万
@@ -24439,7 +24477,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O15" s="16" t="inlineStr">
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $511万
@@ -24448,13 +24486,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $648万
@@ -24462,7 +24500,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $622万
@@ -24470,7 +24508,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $660万
@@ -24478,7 +24516,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $660万
@@ -24486,7 +24524,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $629万
@@ -24494,7 +24532,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 259呎 (1房)
 $620万
@@ -24502,7 +24540,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 410呎 (2房)
 $916万
@@ -24510,7 +24548,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $501万
@@ -24518,7 +24556,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $654万
@@ -24526,7 +24564,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K16" s="16" t="inlineStr">
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $622万
@@ -24534,7 +24572,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L16" s="16" t="inlineStr">
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $619万
@@ -24542,7 +24580,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M16" s="16" t="inlineStr">
+      <c r="M15" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $501万
@@ -24550,7 +24588,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N16" s="16" t="inlineStr">
+      <c r="N15" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $486万
@@ -24558,7 +24596,7 @@
 (20年-08月)</t>
         </is>
       </c>
-      <c r="O16" s="16" t="inlineStr">
+      <c r="O15" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $502万
@@ -24567,13 +24605,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $611万
@@ -24581,7 +24619,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $625万
@@ -24589,7 +24627,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $622万
@@ -24597,7 +24635,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $622万
@@ -24605,7 +24643,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $625万
@@ -24613,7 +24651,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 258呎 (1房)
 $648万
@@ -24621,7 +24659,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 410呎 (2房)
 $760万
@@ -24629,7 +24667,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $492万
@@ -24637,7 +24675,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $650万
@@ -24645,7 +24683,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K17" s="16" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $625万
@@ -24653,7 +24691,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L17" s="16" t="inlineStr">
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $615万
@@ -24661,7 +24699,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M17" s="16" t="inlineStr">
+      <c r="M16" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $498万
@@ -24669,7 +24707,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N17" s="16" t="inlineStr">
+      <c r="N16" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $488万
@@ -24677,7 +24715,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O17" s="16" t="inlineStr">
+      <c r="O16" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $504万
@@ -24686,13 +24724,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $606万
@@ -24700,7 +24738,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $620万
@@ -24708,7 +24746,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $618万
@@ -24716,7 +24754,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $611万
@@ -24724,7 +24762,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $614万
@@ -24732,7 +24770,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 258呎 (1房)
 $611万
@@ -24740,7 +24778,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 411呎 (2房)
 $999万
@@ -24748,7 +24786,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $487万
@@ -24756,7 +24794,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $643万
@@ -24764,7 +24802,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K18" s="16" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $614万
@@ -24772,7 +24810,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L18" s="16" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $610万
@@ -24780,7 +24818,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M18" s="16" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $500万
@@ -24788,7 +24826,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N18" s="16" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $484万
@@ -24796,7 +24834,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O18" s="16" t="inlineStr">
+      <c r="O17" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $500万
@@ -24805,13 +24843,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $596万
@@ -24819,7 +24857,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $609万
@@ -24827,7 +24865,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $613万
@@ -24835,7 +24873,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $613万
@@ -24843,7 +24881,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $609万
@@ -24851,7 +24889,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 259呎 (1房)
 $639万
@@ -24859,7 +24897,7 @@
 (20年-10月)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 411呎 (2房)
 $897万
@@ -24867,7 +24905,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $487万
@@ -24875,7 +24913,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $636万
@@ -24883,7 +24921,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K19" s="16" t="inlineStr">
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $616万
@@ -24891,7 +24929,7 @@
 (20年-06月)</t>
         </is>
       </c>
-      <c r="L19" s="16" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $638万
@@ -24899,7 +24937,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M19" s="16" t="inlineStr">
+      <c r="M18" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $486万
@@ -24907,7 +24945,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N19" s="16" t="inlineStr">
+      <c r="N18" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $476万
@@ -24915,7 +24953,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O19" s="16" t="inlineStr">
+      <c r="O18" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $491万
@@ -24924,13 +24962,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $591万
@@ -24938,7 +24976,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $611万
@@ -24946,7 +24984,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $609万
@@ -24954,7 +24992,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $609万
@@ -24962,7 +25000,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $611万
@@ -24970,7 +25008,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 259呎 (1房)
 $596万
@@ -24978,7 +25016,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 411呎 (2房)
 $985万
@@ -24986,7 +25024,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $480万
@@ -24994,7 +25032,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $627万
@@ -25002,7 +25040,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K20" s="16" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $612万
@@ -25010,7 +25048,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L20" s="16" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $602万
@@ -25018,7 +25056,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M20" s="16" t="inlineStr">
+      <c r="M19" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $487万
@@ -25026,7 +25064,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N20" s="16" t="inlineStr">
+      <c r="N19" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $472万
@@ -25034,7 +25072,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O20" s="16" t="inlineStr">
+      <c r="O19" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $493万
@@ -25043,13 +25081,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $587万
@@ -25057,7 +25095,7 @@
 (20年-10月)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $607万
@@ -25065,7 +25103,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $598万
@@ -25073,7 +25111,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $598万
@@ -25081,7 +25119,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $639万
@@ -25089,7 +25127,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 259呎 (1房)
 $598万
@@ -25097,7 +25135,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 410呎 (2房)
 $999万
@@ -25105,7 +25143,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $471万
@@ -25113,7 +25151,7 @@
 (20年-12月)</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $616万
@@ -25121,7 +25159,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K21" s="16" t="inlineStr">
+      <c r="K20" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $607万
@@ -25129,7 +25167,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L21" s="16" t="inlineStr">
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $598万
@@ -25137,7 +25175,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M21" s="16" t="inlineStr">
+      <c r="M20" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $515万
@@ -25145,7 +25183,7 @@
 (20年-08月)</t>
         </is>
       </c>
-      <c r="N21" s="16" t="inlineStr">
+      <c r="N20" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $469万
@@ -25153,7 +25191,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O21" s="16" t="inlineStr">
+      <c r="O20" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $490万
@@ -25162,13 +25200,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $585万
@@ -25176,7 +25214,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $605万
@@ -25184,7 +25222,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $596万
@@ -25192,7 +25230,7 @@
 (20年-05月)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $602万
@@ -25200,7 +25238,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $598万
@@ -25208,7 +25246,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 258呎 (1房)
 $590万
@@ -25216,7 +25254,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 411呎 (2房)
 $974万
@@ -25224,7 +25262,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $474万
@@ -25232,7 +25270,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $614万
@@ -25240,7 +25278,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K22" s="16" t="inlineStr">
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $599万
@@ -25248,7 +25286,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L22" s="16" t="inlineStr">
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $595万
@@ -25256,7 +25294,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M22" s="16" t="inlineStr">
+      <c r="M21" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $482万
@@ -25264,7 +25302,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N22" s="16" t="inlineStr">
+      <c r="N21" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $472万
@@ -25272,7 +25310,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O22" s="16" t="inlineStr">
+      <c r="O21" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $483万
@@ -25281,13 +25319,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $618万
@@ -25295,7 +25333,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $600万
@@ -25303,7 +25341,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $591万
@@ -25311,7 +25349,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $597万
@@ -25319,7 +25357,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $594万
@@ -25327,7 +25365,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 259呎 (1房)
 $585万
@@ -25335,7 +25373,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 411呎 (2房)
 $977万
@@ -25343,7 +25381,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $496万
@@ -25351,7 +25389,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $635万
@@ -25359,7 +25397,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K23" s="16" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $633万
@@ -25367,7 +25405,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L23" s="16" t="inlineStr">
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $591万
@@ -25375,7 +25413,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M23" s="16" t="inlineStr">
+      <c r="M22" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $479万
@@ -25383,7 +25421,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N23" s="16" t="inlineStr">
+      <c r="N22" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $468万
@@ -25391,7 +25429,7 @@
 (20年-08月)</t>
         </is>
       </c>
-      <c r="O23" s="16" t="inlineStr">
+      <c r="O22" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $515万
@@ -25400,13 +25438,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 256呎 (1房)
 $580万
@@ -25414,7 +25452,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 256呎 (1房)
 $593万
@@ -25422,7 +25460,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 256呎 (1房)
 $622万
@@ -25430,7 +25468,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 256呎 (1房)
 $591万
@@ -25438,7 +25476,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 256呎 (1房)
 $587万
@@ -25446,7 +25484,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 258呎 (1房)
 $579万
@@ -25454,7 +25492,7 @@
 (20年-11月)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 411呎 (2房)
 $977万
@@ -25462,7 +25500,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 198呎 (开放式)
 $465万
@@ -25470,7 +25508,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 267呎 (1房)
 $628万
@@ -25478,7 +25516,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K24" s="16" t="inlineStr">
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>K | 253呎 (1房)
 $626万
@@ -25486,7 +25524,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L24" s="16" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>L | 255呎 (1房)
 $585万
@@ -25494,7 +25532,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M24" s="16" t="inlineStr">
+      <c r="M23" s="20" t="inlineStr">
         <is>
           <t>M | 197呎 (开放式)
 $373万
@@ -25502,7 +25540,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N24" s="16" t="inlineStr">
+      <c r="N23" s="20" t="inlineStr">
         <is>
           <t>N | 193呎 (开放式)
 $458万
@@ -25510,7 +25548,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O24" s="16" t="inlineStr">
+      <c r="O23" s="20" t="inlineStr">
         <is>
           <t>P | 200呎 (开放式)
 $479万
@@ -25519,13 +25557,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 235呎 (1房)
 $500万
@@ -25533,7 +25571,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 235呎 (1房)
 $620万
@@ -25541,7 +25579,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 235呎 (1房)
 $610万
@@ -25549,7 +25587,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 235呎 (1房)
 $625万
@@ -25557,7 +25595,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 235呎 (1房)
 $520万
@@ -25565,7 +25603,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 237呎 (1房)
 $550万
@@ -25573,7 +25611,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 374呎 (2房)
 $975万
@@ -25581,7 +25619,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 178呎 (开放式)
 $380万
@@ -25589,7 +25627,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 243呎 (1房)
 $580万
@@ -25597,7 +25635,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K25" s="16" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>K | 231呎 (1房)
 $640万
@@ -25605,7 +25643,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L25" s="16" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>L | 234呎 (1房)
 $560万
@@ -25613,7 +25651,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M25" s="16" t="inlineStr">
+      <c r="M24" s="20" t="inlineStr">
         <is>
           <t>M | 174呎 (开放式)
 $415万
@@ -25621,7 +25659,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N25" s="16" t="inlineStr">
+      <c r="N24" s="20" t="inlineStr">
         <is>
           <t>N | 171呎 (开放式)
 $485万
@@ -25629,7 +25667,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O25" s="16" t="inlineStr">
+      <c r="O24" s="20" t="inlineStr">
         <is>
           <t>P | 179呎 (开放式)
 $420万
@@ -25640,7 +25678,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -25653,163 +25691,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>利奥坊．曦岸 - 2座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>215 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>214 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 687呎 (3房)
 招标单位
@@ -25817,15 +25855,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 383呎 (1房)
-$1,086万
+$1086万
 $28,368/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 260呎 (2房)
 $739万
@@ -25833,15 +25871,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 657呎 (3房)
-$1,895万
+$1895万
 $28,843/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 321呎 (1房)
 $800万
@@ -25849,7 +25887,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 267呎 (1房)
 $698万
@@ -25857,19 +25895,19 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr"/>
-      <c r="I6" s="17" t="inlineStr"/>
-      <c r="J6" s="17" t="inlineStr"/>
-      <c r="K6" s="17" t="inlineStr"/>
-      <c r="L6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+      <c r="K5" s="21" t="inlineStr"/>
+      <c r="L5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 259呎 (1房)
 $688万
@@ -25877,15 +25915,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
-$1,172万
+$1172万
 $28,379/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $678万
@@ -25893,7 +25931,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $695万
@@ -25901,7 +25939,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $711万
@@ -25909,7 +25947,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $689万
@@ -25917,15 +25955,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 399呎 (2房)
-$1,070万
+$1070万
 $26,807/呎
 (21年-07月)</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 286呎 (1房)
 $776万
@@ -25933,7 +25971,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $420万
@@ -25941,7 +25979,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K7" s="16" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $389万
@@ -25949,7 +25987,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L7" s="16" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $421万
@@ -25958,13 +25996,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 258呎 (1房)
 $676万
@@ -25972,15 +26010,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
-$1,152万
+$1152万
 $27,900/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $667万
@@ -25988,7 +26026,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $698万
@@ -25996,7 +26034,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $706万
@@ -26004,7 +26042,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $678万
@@ -26012,15 +26050,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 399呎 (2房)
-$1,063万
+$1063万
 $26,633/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 286呎 (1房)
 $633万
@@ -26028,7 +26066,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $417万
@@ -26036,7 +26074,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $381万
@@ -26044,7 +26082,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L8" s="16" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $419万
@@ -26053,13 +26091,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 259呎 (1房)
 $658万
@@ -26067,15 +26105,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
-$1,157万
+$1157万
 $28,007/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $669万
@@ -26083,7 +26121,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $693万
@@ -26091,7 +26129,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $709万
@@ -26099,7 +26137,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $673万
@@ -26107,15 +26145,15 @@
 (21年-05月)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 399呎 (2房)
-$1,056万
+$1056万
 $26,460/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 286呎 (1房)
 $750万
@@ -26123,7 +26161,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $375万
@@ -26131,7 +26169,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K9" s="16" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $508万
@@ -26139,7 +26177,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $506万
@@ -26148,13 +26186,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 259呎 (1房)
 $661万
@@ -26162,15 +26200,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
-$1,096万
+$1096万
 $26,529/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 247呎 (1房)
 $653万
@@ -26178,7 +26216,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $677万
@@ -26186,7 +26224,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $692万
@@ -26194,7 +26232,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $660万
@@ -26202,15 +26240,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 399呎 (2房)
-$1,000万
+$1000万
 $25,059/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 286呎 (1房)
 $625万
@@ -26218,7 +26256,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $528万
@@ -26226,7 +26264,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K10" s="16" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $533万
@@ -26234,7 +26272,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L10" s="16" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $530万
@@ -26243,13 +26281,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 258呎 (1房)
 $649万
@@ -26257,15 +26295,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
-$1,114万
+$1114万
 $26,984/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 247呎 (1房)
 $645万
@@ -26273,7 +26311,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $672万
@@ -26281,7 +26319,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $683万
@@ -26289,7 +26327,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $659万
@@ -26297,7 +26335,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 399呎 (2房)
 $997万
@@ -26305,7 +26343,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 287呎 (1房)
 $764万
@@ -26313,7 +26351,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $514万
@@ -26321,7 +26359,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K11" s="16" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $534万
@@ -26329,7 +26367,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L11" s="16" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $527万
@@ -26338,13 +26376,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 258呎 (1房)
 $638万
@@ -26352,15 +26390,15 @@
 (21年-05月)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
-$1,107万
+$1107万
 $26,802/呎
 (22年-03月)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 247呎 (1房)
 $647万
@@ -26368,7 +26406,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $661万
@@ -26376,7 +26414,7 @@
 (21年-04月)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $679万
@@ -26384,7 +26422,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $647万
@@ -26392,7 +26430,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 400呎 (2房)
 $990万
@@ -26400,7 +26438,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 286呎 (1房)
 $750万
@@ -26408,7 +26446,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $527万
@@ -26416,7 +26454,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K12" s="16" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>K | 193呎 (开放式)
 $525万
@@ -26424,7 +26462,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L12" s="16" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $529万
@@ -26433,13 +26471,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 258呎 (1房)
 $641万
@@ -26447,15 +26485,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
-$1,099万
+$1099万
 $26,618/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $636万
@@ -26463,7 +26501,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $664万
@@ -26471,7 +26509,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $661万
@@ -26479,7 +26517,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $650万
@@ -26487,7 +26525,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 400呎 (2房)
 $984万
@@ -26495,7 +26533,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 287呎 (1房)
 $745万
@@ -26503,7 +26541,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $518万
@@ -26511,7 +26549,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K13" s="16" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>K | 193呎 (开放式)
 $522万
@@ -26519,7 +26557,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L13" s="16" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $514万
@@ -26528,13 +26566,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 258呎 (1房)
 $636万
@@ -26542,15 +26580,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
-$1,103万
+$1103万
 $26,715/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $631万
@@ -26558,7 +26596,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $652万
@@ -26566,7 +26604,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $649万
@@ -26574,7 +26612,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $646万
@@ -26582,7 +26620,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 399呎 (2房)
 $967万
@@ -26590,7 +26628,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 287呎 (1房)
 $740万
@@ -26598,7 +26636,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $514万
@@ -26606,7 +26644,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K14" s="16" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $513万
@@ -26614,7 +26652,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L14" s="16" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $511万
@@ -26623,13 +26661,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 258呎 (1房)
 $625万
@@ -26637,15 +26675,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
-$1,084万
+$1084万
 $26,253/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $634万
@@ -26653,7 +26691,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $698万
@@ -26661,7 +26699,7 @@
 (21年-04月)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $652万
@@ -26669,7 +26707,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $641万
@@ -26677,7 +26715,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 400呎 (2房)
 $970万
@@ -26685,7 +26723,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 286呎 (1房)
 $709万
@@ -26693,7 +26731,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $505万
@@ -26701,7 +26739,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K15" s="16" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $509万
@@ -26709,7 +26747,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L15" s="16" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $513万
@@ -26718,13 +26756,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 259呎 (1房)
 $621万
@@ -26732,15 +26770,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
-$1,044万
+$1044万
 $25,287/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $622万
@@ -26748,7 +26786,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $652万
@@ -26756,7 +26794,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $647万
@@ -26764,7 +26802,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $637万
@@ -26772,7 +26810,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 400呎 (2房)
 $964万
@@ -26780,7 +26818,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 287呎 (1房)
 $733万
@@ -26788,7 +26826,7 @@
 (21年-09月)</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $501万
@@ -26796,7 +26834,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K16" s="16" t="inlineStr">
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $516万
@@ -26804,7 +26842,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L16" s="16" t="inlineStr">
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $504万
@@ -26813,13 +26851,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 258呎 (1房)
 $623万
@@ -26827,15 +26865,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
-$1,047万
+$1047万
 $25,342/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $625万
@@ -26843,7 +26881,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $649万
@@ -26851,7 +26889,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $643万
@@ -26859,7 +26897,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $632万
@@ -26867,7 +26905,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 400呎 (2房)
 $957万
@@ -26875,7 +26913,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 287呎 (1房)
 $725万
@@ -26883,7 +26921,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $498万
@@ -26891,7 +26929,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K17" s="16" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $502万
@@ -26899,7 +26937,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L17" s="16" t="inlineStr">
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $495万
@@ -26908,13 +26946,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 258呎 (1房)
 $619万
@@ -26922,15 +26960,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
-$1,021万
+$1021万
 $24,715/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $648万
@@ -26938,7 +26976,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $633万
@@ -26946,7 +26984,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $657万
@@ -26954,7 +26992,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $617万
@@ -26962,7 +27000,7 @@
 (21年-02月)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 399呎 (2房)
 $953万
@@ -26970,7 +27008,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 287呎 (1房)
 $717万
@@ -26978,7 +27016,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $519万
@@ -26986,7 +27024,7 @@
 (20年-07月)</t>
         </is>
       </c>
-      <c r="K18" s="16" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $497万
@@ -26994,7 +27032,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L18" s="16" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $521万
@@ -27003,13 +27041,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 258呎 (1房)
 $615万
@@ -27017,15 +27055,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
-$1,006万
+$1006万
 $24,359/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $646万
@@ -27033,7 +27071,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $624万
@@ -27041,7 +27079,7 @@
 (21年-05月)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $665万
@@ -27049,7 +27087,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $608万
@@ -27057,7 +27095,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 400呎 (2房)
 $920万
@@ -27065,7 +27103,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 287呎 (1房)
 $684万
@@ -27073,7 +27111,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $487万
@@ -27081,7 +27119,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K19" s="16" t="inlineStr">
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $491万
@@ -27089,7 +27127,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L19" s="16" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $516万
@@ -27098,13 +27136,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 258呎 (1房)
 $604万
@@ -27112,15 +27150,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
-$1,042万
+$1042万
 $25,232/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $596万
@@ -27128,7 +27166,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $620万
@@ -27136,7 +27174,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $643万
@@ -27144,7 +27182,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $604万
@@ -27152,7 +27190,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 400呎 (2房)
 $923万
@@ -27160,7 +27198,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 286呎 (1房)
 $712万
@@ -27168,7 +27206,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $475万
@@ -27176,7 +27214,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K20" s="16" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $484万
@@ -27184,7 +27222,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L20" s="16" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $483万
@@ -27193,13 +27231,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 258呎 (1房)
 $599万
@@ -27207,7 +27245,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
 $991万
@@ -27215,7 +27253,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $598万
@@ -27223,7 +27261,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $622万
@@ -27231,7 +27269,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $638万
@@ -27239,7 +27277,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $606万
@@ -27247,7 +27285,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 400呎 (2房)
 $916万
@@ -27255,7 +27293,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 286呎 (1房)
 $676万
@@ -27263,7 +27301,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $476万
@@ -27271,7 +27309,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K21" s="16" t="inlineStr">
+      <c r="K20" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $475万
@@ -27279,7 +27317,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L21" s="16" t="inlineStr">
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $505万
@@ -27288,13 +27326,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 258呎 (1房)
 $597万
@@ -27302,7 +27340,7 @@
 (21年-01月)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
 $977万
@@ -27310,7 +27348,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $596万
@@ -27318,7 +27356,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $620万
@@ -27326,7 +27364,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $636万
@@ -27334,7 +27372,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $604万
@@ -27342,7 +27380,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 399呎 (2房)
 $913万
@@ -27350,7 +27388,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 287呎 (1房)
 $705万
@@ -27358,7 +27396,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $475万
@@ -27366,7 +27404,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K22" s="16" t="inlineStr">
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $479万
@@ -27374,7 +27412,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L22" s="16" t="inlineStr">
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $472万
@@ -27383,13 +27421,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 258呎 (1房)
 $624万
@@ -27397,7 +27435,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
 $980万
@@ -27405,7 +27443,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 247呎 (1房)
 $623万
@@ -27413,7 +27451,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $615万
@@ -27421,7 +27459,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $631万
@@ -27429,7 +27467,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $615万
@@ -27437,7 +27475,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 400呎 (2房)
 $906万
@@ -27445,7 +27483,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 286呎 (1房)
 $668万
@@ -27453,7 +27491,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $471万
@@ -27461,7 +27499,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K23" s="16" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $470万
@@ -27469,7 +27507,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L23" s="16" t="inlineStr">
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $474万
@@ -27478,13 +27516,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 259呎 (1房)
 $617万
@@ -27492,7 +27530,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 413呎 (2房)
 $971万
@@ -27500,7 +27538,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $584万
@@ -27508,7 +27546,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 257呎 (1房)
 $602万
@@ -27516,7 +27554,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 257呎 (1房)
 $596万
@@ -27524,7 +27562,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 257呎 (1房)
 $614万
@@ -27532,7 +27570,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 399呎 (2房)
 $896万
@@ -27540,7 +27578,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 287呎 (1房)
 $691万
@@ -27548,7 +27586,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 193呎 (开放式)
 $461万
@@ -27556,7 +27594,7 @@
 (20年-05月)</t>
         </is>
       </c>
-      <c r="K24" s="16" t="inlineStr">
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>K | 194呎 (开放式)
 $465万
@@ -27564,7 +27602,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L24" s="16" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>L | 197呎 (开放式)
 $469万
@@ -27573,13 +27611,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 237呎 (1房)
 $630万
@@ -27587,7 +27625,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 376呎 (2房)
 $875万
@@ -27595,7 +27633,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 226呎 (1房)
 $610万
@@ -27603,7 +27641,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 236呎 (1房)
 $630万
@@ -27611,7 +27649,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 236呎 (1房)
 $520万
@@ -27619,7 +27657,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 236呎 (1房)
 $618万
@@ -27627,7 +27665,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 362呎 (2房)
 $888万
@@ -27635,7 +27673,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 265呎 (1房)
 $698万
@@ -27643,7 +27681,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 171呎 (开放式)
 $510万
@@ -27651,7 +27689,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K25" s="16" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>K | 172呎 (开放式)
 $512万
@@ -27659,7 +27697,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L25" s="16" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>L | 174呎 (开放式)
 $490万
@@ -27670,7 +27708,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
